--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -4938,7 +4938,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -4938,7 +4938,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -4938,7 +4938,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -4938,7 +4938,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -4938,7 +4938,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -4938,7 +4938,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -4938,7 +4938,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -4938,7 +4938,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251214_201431.xlsx
@@ -4938,7 +4938,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
